--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 10:45</t>
+          <t>Generated 29 Mar 2026 11:04</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -478,6 +478,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | A Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated 29 Mar 2026 11:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>DAVID ALSTON</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>07730771564</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>alstondr@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>CATH PEARSON</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07803 177572</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>cath.pearson@ntlworld.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CLIFF CHURCH</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07929 207152</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>cliffchurch@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>JACQUIE CONWAY</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07900333359</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>jacquie.conway@outlook.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>JANE DOW</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>JANE VINCENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>07787 824330</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>thevincents365@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>JEREMY HILLAGE</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>07881314229</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>jeremyhillage@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>MIKE THORNLEY</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>07786 094178</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>mike33lufc@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>PAUL HAMPSHIRE</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>07850 810133</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>paul.hampshire63@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>PETER GRANT</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>07736 252655</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>petergrant471@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>RICHARD VALLIS</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>07817 051360</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Rbvallis@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SALLY CHARLTON</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>07724 103325</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>sallycharlton22@btinternet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SIAN THOMAS</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+447740943585</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>siannie.thomas@icloud.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SUE WHITE</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>01256 893013</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>susan582009@hotmail.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -492,14 +944,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | A Team</t>
+          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | B Team</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -543,7 +995,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>DAVID ALSTON</t>
+          <t>EDWARD WOODS</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -554,12 +1006,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07730771564</t>
+          <t>07816759110</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>alstondr@hotmail.com</t>
+          <t>edwardanthonywoods@gmail.com</t>
         </is>
       </c>
     </row>
@@ -567,23 +1019,23 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CATH PEARSON</t>
+          <t>ALEX KATON</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07803 177572</t>
+          <t>07568 560257</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>cath.pearson@ntlworld.com</t>
+          <t>alex.katon@hotmail.com</t>
         </is>
       </c>
     </row>
@@ -591,7 +1043,7 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CLIFF CHURCH</t>
+          <t>CHRIS EZRA</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
@@ -602,12 +1054,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07929 207152</t>
+          <t>07956 261566</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>cliffchurch@hotmail.com</t>
+          <t>casabella@btinternet.com</t>
         </is>
       </c>
     </row>
@@ -615,7 +1067,7 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>JACQUIE CONWAY</t>
+          <t>DIANE DOYLE</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
@@ -626,12 +1078,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>07900333359</t>
+          <t>07944 757679</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>jacquie.conway@outlook.com</t>
+          <t>dianeldoyle@gmail.com</t>
         </is>
       </c>
     </row>
@@ -639,39 +1091,51 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>JANE DOW</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>JILL PENTON</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>No Match</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07845 144977</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>jillian.penton@virginmedia.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>JANE VINCENT</t>
+          <t>KATHERINE ROGERS</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>07787 824330</t>
+          <t>07885 304570</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>thevincents365@gmail.com</t>
+          <t>katherinerogers10@gmail.com</t>
         </is>
       </c>
     </row>
@@ -679,7 +1143,7 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>JEREMY HILLAGE</t>
+          <t>NICK WARD</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
@@ -690,12 +1154,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>07881314229</t>
+          <t>07747 897885</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>jeremyhillage@gmail.com</t>
+          <t>nickward010@gmail.com</t>
         </is>
       </c>
     </row>
@@ -703,23 +1167,23 @@
       <c r="A11" s="5" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>MIKE THORNLEY</t>
+          <t>PAULINE SNELL</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>07786 094178</t>
+          <t>07877300234</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>mike33lufc@gmail.com</t>
+          <t>psnell66@gmail.com</t>
         </is>
       </c>
     </row>
@@ -727,23 +1191,27 @@
       <c r="A12" s="5" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>PAUL HAMPSHIRE</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
+          <t>PETE SMITH</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>07850 810133</t>
+          <t>07955644682</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>paul.hampshire63@hotmail.com</t>
+          <t>Peterrcsmith@hotmail.co.uk</t>
         </is>
       </c>
     </row>
@@ -751,7 +1219,7 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>PETER GRANT</t>
+          <t>STUART ABERDEEN</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
@@ -762,12 +1230,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07736 252655</t>
+          <t>07900247090</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>petergrant471@gmail.com</t>
+          <t>stuaberdeen@live.co.uk</t>
         </is>
       </c>
     </row>
@@ -775,7 +1243,7 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>RICHARD VALLIS</t>
+          <t>VAL TALBOT</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
@@ -786,12 +1254,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>07817 051360</t>
+          <t>07767 072546</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Rbvallis@gmail.com</t>
+          <t>valerie.talbot@ntlworld.com</t>
         </is>
       </c>
     </row>
@@ -799,7 +1267,7 @@
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>SALLY CHARLTON</t>
+          <t>VERNA DUFON</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
@@ -810,89 +1278,57 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>07724 103325</t>
+          <t>07816 137440</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>sallycharlton22@btinternet.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>SIAN THOMAS</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>+447740943585</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>siannie.thomas@icloud.com</t>
+          <t>verna.dufon@ntlworld.com</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SUE WHITE</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>01256 893013</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>susan582009@hotmail.co.uk</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -900,13 +1336,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -920,14 +1356,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | B Team</t>
+          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | C Team</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -971,7 +1407,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>EDWARD WOODS</t>
+          <t>SUSAN GILCHRIST</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -982,12 +1418,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>07816759110</t>
+          <t>07802 574286</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>edwardanthonywoods@gmail.com</t>
+          <t>mrs.susan.gilchrist@gmail.com</t>
         </is>
       </c>
     </row>
@@ -995,10 +1431,14 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ALEX KATON</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+          <t>CAROLE -ANN HARRISON</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1006,12 +1446,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07568 560257</t>
+          <t>07799624958</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>alex.katon@hotmail.com</t>
+          <t>cah.dbf@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1459,7 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CHRIS EZRA</t>
+          <t>CLAIRE TAYLOR</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
@@ -1030,12 +1470,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07956 261566</t>
+          <t>07792410799</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>casabella@btinternet.com</t>
+          <t>clairechicago1@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1483,7 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>DIANE DOYLE</t>
+          <t>DAVID HENSHAW</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
@@ -1054,12 +1494,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>07944 757679</t>
+          <t>07941347869</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>dianeldoyle@gmail.com</t>
+          <t>helendavidhenshaw@yahoo.co.uk</t>
         </is>
       </c>
     </row>
@@ -1067,27 +1507,23 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>JILL PENTON</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Fuzzy</t>
-        </is>
-      </c>
+          <t>DAVID WHITE</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07845 144977</t>
+          <t>07712812277</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>jillian.penton@virginmedia.com</t>
+          <t>davidiwhite76@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1095,23 +1531,27 @@
       <c r="A9" s="5" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>KATHERINE ROGERS</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
+          <t>JAX S BROWN</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>07885 304570</t>
+          <t>07889433872</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>katherinerogers10@gmail.com</t>
+          <t>jaxsb1962@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1559,7 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>NICK WARD</t>
+          <t>JESSICA PALMER</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
@@ -1130,12 +1570,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>07747 897885</t>
+          <t>07962260856</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>nickward010@gmail.com</t>
+          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
         </is>
       </c>
     </row>
@@ -1143,23 +1583,23 @@
       <c r="A11" s="5" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>PAULINE SNELL</t>
+          <t>JONTY MASTON</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>07877300234</t>
+          <t>07460 630363</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>psnell66@gmail.com</t>
+          <t>j.maston@btinternet.com</t>
         </is>
       </c>
     </row>
@@ -1167,23 +1607,23 @@
       <c r="A12" s="5" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>PETE SMITH</t>
+          <t>PAUL TREACY</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>07955644682</t>
+          <t>07746 038449</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Peterrcsmith@hotmail.co.uk</t>
+          <t>paultreacy01@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1191,23 +1631,23 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>STUART ABERDEEN</t>
+          <t>ROGER BARNACLE</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>07900247090</t>
+          <t>01256702931</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>stuaberdeen@live.co.uk</t>
+          <t>rbarnacle1@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1215,23 +1655,23 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>VAL TALBOT</t>
+          <t>TIM READ</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>07767 072546</t>
+          <t>07836652532</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>valerie.talbot@ntlworld.com</t>
+          <t>t.read423@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1239,30 +1679,34 @@
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>VERNA DUFON</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
+          <t>TRISH HARRIS</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>07816 137440</t>
+          <t>07801966381</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>verna.dufon@ntlworld.com</t>
+          <t>harrisstrish@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1276,29 +1720,45 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1312,14 +1772,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | C Team</t>
+          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | Reserves</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:04</t>
+          <t>Generated 29 Mar 2026 11:10</t>
         </is>
       </c>
     </row>
@@ -1356,30 +1816,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>SUSAN GILCHRIST</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>07802 574286</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>mrs.susan.gilchrist@gmail.com</t>
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>DEREK CARDER</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>07806 777845</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>derekcarder@rocketmail.com</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1843,7 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CAROLE -ANN HARRISON</t>
+          <t>GEORGINA RICHES</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
@@ -1398,12 +1854,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07799624958</t>
+          <t>07710475970</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>cah.dbf@gmail.com</t>
+          <t>fam.riches@btinternet.com</t>
         </is>
       </c>
     </row>
@@ -1411,10 +1867,14 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CLAIRE TAYLOR</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+          <t>JON CLACKETT</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Not Signed Up</t>
@@ -1422,12 +1882,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>07792410799</t>
+          <t>07799 435600</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>clairechicago1@gmail.com</t>
+          <t>jonathanclackett02@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1435,23 +1895,23 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>DAVID HENSHAW</t>
+          <t>MAEW TATAM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Not Signed Up</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>07941347869</t>
+          <t>07885719965</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>helendavidhenshaw@yahoo.co.uk</t>
+          <t>walanda@hotmail.com</t>
         </is>
       </c>
     </row>
@@ -1459,23 +1919,27 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>DAVID WHITE</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>MO CLACKETT</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07712812277</t>
+          <t>07703 196204</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>davidiwhite76@gmail.com</t>
+          <t>moclackett@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1483,23 +1947,23 @@
       <c r="A9" s="5" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>JAX S BROWN</t>
+          <t>RAY RISTOW</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>07889433872</t>
+          <t>07801107701</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>jaxsb1962@gmail.com</t>
+          <t>ray.ristow@outlook.com</t>
         </is>
       </c>
     </row>
@@ -1507,400 +1971,12 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>JESSICA PALMER</t>
+          <t>TIM PRESLAND</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>07962260856</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>JONTY MASTON</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>07460 630363</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>j.maston@btinternet.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>PAUL TREACY</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>07746 038449</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>paultreacy01@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>ROGER BARNACLE</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>01256702931</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>rbarnacle1@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>TIM READ</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>07836652532</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>t.read423@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>TRISH HARRIS</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>07801966381</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>harrisstrish@outlook.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Avondale Tennis Club | VETS TEAMS 2026 Summer | Reserves</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated 29 Mar 2026 11:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>DEREK CARDER</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>07806 777845</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>derekcarder@rocketmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>GEORGINA RICHES</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>07710475970</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>fam.riches@btinternet.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>JON CLACKETT</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>07799 435600</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>jonathanclackett02@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MAEW TATAM</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>07885719965</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>walanda@hotmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>MO CLACKETT</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>07703 196204</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>moclackett@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>RAY RISTOW</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>07801107701</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>ray.ristow@outlook.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>TIM PRESLAND</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
           <t>Senior</t>
         </is>
       </c>
@@ -1918,7 +1994,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
         </is>
       </c>
     </row>
@@ -1932,17 +2008,33 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>*** Fuzzy = matched by the cautious fuzzy fallback after exact and override-based matching failed.</t>
+          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -892,26 +892,34 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
@@ -930,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -951,7 +959,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1304,29 +1312,37 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -1342,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1363,7 +1379,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1720,29 +1736,37 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -1758,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1779,7 +1803,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:10</t>
+          <t>Generated 29 Mar 2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2008,31 +2032,39 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>*** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>**** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>***** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 11:15</t>
+          <t>Generated 29 Mar 2026 12:50</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -646,14 +646,26 @@
           <t>JANE DOW</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>No Match</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+447721967512</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>janeatimmis@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -713,7 +725,7 @@
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -959,7 +971,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1815,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 29 Mar 2026 12:50</t>
+          <t>Generated 30 Mar 2026 14:35</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 30 Mar 2026 14:35</t>
+          <t>Generated 31 Mar 2026 15:53</t>
         </is>
       </c>
     </row>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -107,10 +107,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>01256 893013</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>susan582009@hotmail.co.uk</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -929,8 +929,15 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
@@ -939,6 +946,7 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -950,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -971,7 +979,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1058,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>07568 560257</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>alex.katon@hotmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1158,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>07885 304570</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>katherinerogers10@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1349,11 +1357,19 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
@@ -1370,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1391,7 +1407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1614,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>07962260856</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -1773,11 +1789,19 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
@@ -1794,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1815,7 +1839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 31 Mar 2026 15:53</t>
+          <t>Generated 01 Apr 2026 09:52</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1994,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>07703 196204</t>
+          <t>No Consent</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>moclackett@gmail.com</t>
+          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2069,8 +2093,15 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A13:F13"/>
@@ -2078,6 +2109,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -42,7 +42,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="001F1F1F"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -478,15 +478,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -499,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -516,22 +517,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -546,10 +552,14 @@
           <t>DAVID ALSTON</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -562,6 +572,7 @@
           <t>alstondr@hotmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -570,10 +581,14 @@
           <t>CATH PEARSON</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -586,6 +601,7 @@
           <t>cath.pearson@ntlworld.com</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -594,10 +610,14 @@
           <t>CLIFF CHURCH</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -610,6 +630,7 @@
           <t>cliffchurch@hotmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -620,22 +641,27 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>07900333359</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>jacquie.conway@outlook.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>07900333359</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>jacquie.conway@outlook.com</t>
         </is>
       </c>
     </row>
@@ -648,22 +674,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+447721967512</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>janeatimmis@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+447721967512</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>janeatimmis@gmail.com</t>
         </is>
       </c>
     </row>
@@ -674,10 +705,14 @@
           <t>JANE VINCENT</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -690,6 +725,7 @@
           <t>thevincents365@gmail.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -698,10 +734,14 @@
           <t>JEREMY HILLAGE</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -714,6 +754,7 @@
           <t>jeremyhillage@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -722,10 +763,14 @@
           <t>MIKE THORNLEY</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -738,6 +783,7 @@
           <t>mike33lufc@gmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -746,10 +792,14 @@
           <t>PAUL HAMPSHIRE</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -762,6 +812,7 @@
           <t>paul.hampshire63@hotmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -770,10 +821,14 @@
           <t>PETER GRANT</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -786,6 +841,7 @@
           <t>petergrant471@gmail.com</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -794,10 +850,14 @@
           <t>RICHARD VALLIS</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -810,6 +870,7 @@
           <t>Rbvallis@gmail.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -818,10 +879,14 @@
           <t>SALLY CHARLTON</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -834,6 +899,7 @@
           <t>sallycharlton22@btinternet.com</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
@@ -842,10 +908,14 @@
           <t>SIAN THOMAS</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -858,6 +928,7 @@
           <t>siannie.thomas@icloud.com</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
@@ -868,85 +939,90 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>01256 893013</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>susan582009@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -958,15 +1034,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -979,7 +1056,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -996,22 +1073,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1026,10 +1108,14 @@
           <t>EDWARD WOODS</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1042,6 +1128,7 @@
           <t>edwardanthonywoods@gmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1050,22 +1137,27 @@
           <t>ALEX KATON</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07568 560257</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>alex.katon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -1074,10 +1166,14 @@
           <t>CHRIS EZRA</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1090,6 +1186,7 @@
           <t>casabella@btinternet.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -1098,10 +1195,14 @@
           <t>DIANE DOYLE</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1114,6 +1215,7 @@
           <t>dianeldoyle@gmail.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1124,22 +1226,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07845 144977</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>jillian.penton@virginmedia.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>07845 144977</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>jillian.penton@virginmedia.com</t>
         </is>
       </c>
     </row>
@@ -1150,22 +1257,27 @@
           <t>KATHERINE ROGERS</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07885 304570</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>katherinerogers10@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1174,10 +1286,14 @@
           <t>NICK WARD</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1190,6 +1306,7 @@
           <t>nickward010@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1198,10 +1315,14 @@
           <t>PAULINE SNELL</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1214,6 +1335,7 @@
           <t>psnell66@gmail.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1224,22 +1346,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>07955644682</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Peterrcsmith@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>07955644682</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Peterrcsmith@hotmail.co.uk</t>
         </is>
       </c>
     </row>
@@ -1250,10 +1377,14 @@
           <t>STUART ABERDEEN</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1266,6 +1397,7 @@
           <t>stuaberdeen@live.co.uk</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1274,10 +1406,14 @@
           <t>VAL TALBOT</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1290,6 +1426,7 @@
           <t>valerie.talbot@ntlworld.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -1298,10 +1435,14 @@
           <t>VERNA DUFON</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1314,67 +1455,68 @@
           <t>verna.dufon@ntlworld.com</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1386,15 +1528,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1407,7 +1550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1567,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1454,10 +1602,14 @@
           <t>SUSAN GILCHRIST</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1470,6 +1622,7 @@
           <t>mrs.susan.gilchrist@gmail.com</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1480,22 +1633,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>07799624958</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>cah.dbf@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>07799624958</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>cah.dbf@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1506,10 +1664,14 @@
           <t>CLAIRE TAYLOR</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1522,6 +1684,7 @@
           <t>clairechicago1@gmail.com</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -1530,10 +1693,14 @@
           <t>DAVID HENSHAW</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1546,6 +1713,7 @@
           <t>helendavidhenshaw@yahoo.co.uk</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1554,10 +1722,14 @@
           <t>DAVID WHITE</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1570,6 +1742,7 @@
           <t>davidiwhite76@gmail.com</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1580,22 +1753,27 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>07889433872</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>jaxsb1962@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>Override</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>07889433872</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>jaxsb1962@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1606,22 +1784,27 @@
           <t>JESSICA PALMER</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
+          <t>07962260856</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>No Consent</t>
-        </is>
-      </c>
+          <t>JESSICA.PALMER@FLITEPARTNERS.COM</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1630,10 +1813,14 @@
           <t>JONTY MASTON</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1646,6 +1833,7 @@
           <t>j.maston@btinternet.com</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1654,10 +1842,14 @@
           <t>PAUL TREACY</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1670,6 +1862,7 @@
           <t>paultreacy01@gmail.com</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1678,10 +1871,14 @@
           <t>ROGER BARNACLE</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1694,6 +1891,7 @@
           <t>rbarnacle1@gmail.com</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1702,10 +1900,14 @@
           <t>TIM READ</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1718,6 +1920,7 @@
           <t>t.read423@gmail.com</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
@@ -1728,85 +1931,90 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>07801966381</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>harrisstrish@outlook.com</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
           <t>Fuzzy</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>07801966381</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>harrisstrish@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1818,15 +2026,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1839,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 01 Apr 2026 09:52</t>
+          <t>Generated 02 Apr 2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1856,22 +2065,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Match</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1882,10 +2096,14 @@
           <t>DEREK CARDER</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1898,6 +2116,7 @@
           <t>derekcarder@rocketmail.com</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
@@ -1906,10 +2125,14 @@
           <t>GEORGINA RICHES</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1922,6 +2145,7 @@
           <t>fam.riches@btinternet.com</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -1932,22 +2156,27 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>07799 435600</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>jonathanclackett02@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Not Signed Up</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>07799 435600</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>jonathanclackett02@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1958,10 +2187,14 @@
           <t>MAEW TATAM</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Not Signed Up</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Not Signed Up</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1974,6 +2207,7 @@
           <t>walanda@hotmail.com</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
@@ -1984,22 +2218,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>07703 196204</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>moclackett@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Nickname</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>No Consent</t>
         </is>
       </c>
     </row>
@@ -2010,10 +2249,14 @@
           <t>RAY RISTOW</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2026,6 +2269,7 @@
           <t>ray.ristow@outlook.com</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
@@ -2034,10 +2278,14 @@
           <t>TIM PRESLAND</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2050,67 +2298,68 @@
           <t>timpresland@gmail.com</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>* Not Signed Up = exact or resolved name matched in club records, but no current paid 2026 membership was found.</t>
+          <t>* Consent: No means the captain may use the phone/email for team management, but may not pass it on to anyone else.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>** No Match = no unique exact-name match was found in current club member/contact records.</t>
+          <t>** Not Signed Up = no current membership was found.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>*** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
+          <t>*** No Match = no unique exact-name match was found in current club member/contact records.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>**** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
+          <t>**** Best Fit = one row was chosen from several exact-name candidates using the best available contact evidence.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>***** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
+          <t>***** Override = resolved by an explicit override; this usually represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>****** Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
+          <t>****** Nickname = resolved by a short-name or nickname rule; this may also represent a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>******* No Consent = the current contact record does not allow contact details to be shared, so phone and email are withheld.</t>
+          <t>******* Fuzzy = resolved by the cautious fuzzy fallback; this represents a typo or misspelling in the source data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
+++ b/Teams/generated/VETS  TEAMS 2026 SUMMER - Contact Lists.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 02 Apr 2026 11:51</t>
+          <t>Generated 02 Apr 2026 14:17</t>
         </is>
       </c>
     </row>
